--- a/data/gravel/Sanitas Node Cambium Ti 2025.xlsx
+++ b/data/gravel/Sanitas Node Cambium Ti 2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87A9F37F-01B6-6441-B4E9-DD822251E21B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4774A358-C411-D848-8324-0CC4BFAA261E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12540" yWindow="500" windowWidth="28800" windowHeight="15560" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15560" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/data/gravel/Sanitas Node Cambium Ti 2025.xlsx
+++ b/data/gravel/Sanitas Node Cambium Ti 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4774A358-C411-D848-8324-0CC4BFAA261E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D045E1F-21F7-D346-8CA1-5C77939DB5A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15560" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="126">
   <si>
     <t>brand</t>
   </si>
@@ -393,6 +393,24 @@
   </si>
   <si>
     <t>hardtail</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -807,7 +825,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V77"/>
+  <dimension ref="A1:V83"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" style="2" customWidth="1"/>
@@ -1818,153 +1836,183 @@
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
-        <v>45</v>
+        <v>121</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B55" s="2">
-        <v>31.6</v>
+        <v>122</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B56" s="2" t="s">
-        <v>72</v>
+        <v>123</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B57" s="2">
-        <v>42</v>
+        <v>124</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
-        <v>49</v>
+        <v>125</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
-        <v>50</v>
+        <v>44</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
-        <v>52</v>
+        <v>46</v>
+      </c>
+      <c r="B61" s="2">
+        <v>31.6</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>118</v>
+        <v>72</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B63" s="2" t="s">
-        <v>86</v>
+        <v>48</v>
+      </c>
+      <c r="B63" s="2">
+        <v>42</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
-        <v>59</v>
+        <v>53</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
-        <v>60</v>
+        <v>54</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="B73" s="2">
-        <v>3450</v>
+        <v>58</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B79" s="2">
+        <v>3450</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A80" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A81" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A82" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="B76" s="2" t="s">
+      <c r="B82" s="2" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A77" s="14" t="s">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A83" s="14" t="s">
         <v>88</v>
       </c>
-      <c r="B77" s="14" t="s">
+      <c r="B83" s="14" t="s">
         <v>89</v>
       </c>
     </row>

--- a/data/gravel/Sanitas Node Cambium Ti 2025.xlsx
+++ b/data/gravel/Sanitas Node Cambium Ti 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11122"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D045E1F-21F7-D346-8CA1-5C77939DB5A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60EF1BC9-A1EF-9042-8B3E-58C1784ED741}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15560" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4780" yWindow="2320" windowWidth="28800" windowHeight="15560" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="127">
   <si>
     <t>brand</t>
   </si>
@@ -254,12 +254,6 @@
     <t>yes</t>
   </si>
   <si>
-    <t>front_center</t>
-  </si>
-  <si>
-    <t>trail</t>
-  </si>
-  <si>
     <t>Sanitas</t>
   </si>
   <si>
@@ -383,9 +377,6 @@
     <t>https://images.squarespace-cdn.com/content/v1/683892ca9490732d748fc31b/7ad01fa6-3c07-451a-8f9f-ef37c626b985/ADA457B7-C085-4E49-AE13-0F5453D3B78A.jpeg?format=2500w</t>
   </si>
   <si>
-    <t>a8:g36</t>
-  </si>
-  <si>
     <t>threaded 73</t>
   </si>
   <si>
@@ -411,6 +402,18 @@
   </si>
   <si>
     <t>fork_material</t>
+  </si>
+  <si>
+    <t>fork_sag</t>
+  </si>
+  <si>
+    <t>100-120</t>
+  </si>
+  <si>
+    <t>a8:g35</t>
+  </si>
+  <si>
+    <t>est is 44</t>
   </si>
 </sst>
 </file>
@@ -825,7 +828,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V83"/>
+  <dimension ref="A1:V82"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" style="2" customWidth="1"/>
@@ -839,7 +842,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.3">
@@ -847,7 +850,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.3">
@@ -871,12 +874,12 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.3">
       <c r="B6" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.3">
@@ -884,7 +887,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
     </row>
     <row r="8" spans="1:22" ht="22" x14ac:dyDescent="0.3">
@@ -892,22 +895,22 @@
         <v>6</v>
       </c>
       <c r="B8" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="D8" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="C8" s="11" t="s">
+      <c r="E8" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="F8" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="D8" s="11" t="s">
+      <c r="G8" s="11" t="s">
         <v>93</v>
-      </c>
-      <c r="E8" s="11" t="s">
-        <v>113</v>
-      </c>
-      <c r="F8" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="G8" s="11" t="s">
-        <v>95</v>
       </c>
       <c r="H8" s="11"/>
       <c r="I8" s="7"/>
@@ -930,7 +933,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C9" s="12">
         <v>590</v>
@@ -966,7 +969,7 @@
         <v>11</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C10" s="12">
         <v>67.5</v>
@@ -1002,7 +1005,7 @@
         <v>8</v>
       </c>
       <c r="B11" s="12" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C11" s="12">
         <v>74</v>
@@ -1035,10 +1038,10 @@
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C12" s="2">
         <f>VALUE(LEFT(H12,3))</f>
@@ -1061,19 +1064,19 @@
         <v>457</v>
       </c>
       <c r="H12" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="I12" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="J12" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="I12" s="12" t="s">
+      <c r="K12" s="12" t="s">
         <v>98</v>
       </c>
-      <c r="J12" s="12" t="s">
+      <c r="L12" s="12" t="s">
         <v>99</v>
-      </c>
-      <c r="K12" s="12" t="s">
-        <v>100</v>
-      </c>
-      <c r="L12" s="12" t="s">
-        <v>101</v>
       </c>
       <c r="M12" s="10"/>
       <c r="N12" s="10"/>
@@ -1127,7 +1130,7 @@
         <v>10</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C14" s="12">
         <v>100</v>
@@ -1163,7 +1166,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C15" s="2">
         <f>VALUE(LEFT(H15,3))</f>
@@ -1186,19 +1189,19 @@
         <v>445</v>
       </c>
       <c r="H15" s="12" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="I15" s="12" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="J15" s="12" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="K15" s="12" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="L15" s="12" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="M15" s="8"/>
       <c r="N15" s="5"/>
@@ -1214,7 +1217,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C16" s="12">
         <v>57.5</v>
@@ -1247,10 +1250,10 @@
     </row>
     <row r="17" spans="1:21" ht="22" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C17" s="12">
         <v>320.5</v>
@@ -1286,7 +1289,7 @@
         <v>18</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C18" s="12">
         <v>780</v>
@@ -1322,7 +1325,7 @@
         <v>17</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C19" s="12">
         <v>416.8</v>
@@ -1359,7 +1362,7 @@
         <v>16</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C20" s="12">
         <v>593.20000000000005</v>
@@ -1393,10 +1396,10 @@
     </row>
     <row r="21" spans="1:21" ht="22" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C21" s="8">
         <v>2.4</v>
@@ -1431,7 +1434,7 @@
         <v>19</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C22" s="13">
         <v>1122.5</v>
@@ -1463,10 +1466,10 @@
     </row>
     <row r="23" spans="1:21" ht="22" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C23" s="2">
         <v>100</v>
@@ -1499,7 +1502,7 @@
     </row>
     <row r="24" spans="1:21" ht="22" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>12</v>
+        <v>123</v>
       </c>
       <c r="B24" s="9"/>
       <c r="H24" s="13"/>
@@ -1518,9 +1521,26 @@
     </row>
     <row r="25" spans="1:21" ht="22" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I25" s="8"/>
+        <v>12</v>
+      </c>
+      <c r="B25" s="9"/>
+      <c r="C25" s="2">
+        <v>503.7</v>
+      </c>
+      <c r="D25" s="2">
+        <v>503.7</v>
+      </c>
+      <c r="E25" s="2">
+        <v>503.7</v>
+      </c>
+      <c r="F25" s="2">
+        <v>530</v>
+      </c>
+      <c r="G25" s="2">
+        <v>530</v>
+      </c>
+      <c r="H25" s="13"/>
+      <c r="I25" s="7"/>
       <c r="J25" s="8"/>
       <c r="K25" s="8"/>
       <c r="L25" s="8"/>
@@ -1535,9 +1555,26 @@
     </row>
     <row r="26" spans="1:21" ht="22" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="H26" s="8"/>
+        <v>13</v>
+      </c>
+      <c r="C26" s="2">
+        <v>44</v>
+      </c>
+      <c r="D26" s="2">
+        <v>44</v>
+      </c>
+      <c r="E26" s="2">
+        <v>44</v>
+      </c>
+      <c r="F26" s="2">
+        <v>44</v>
+      </c>
+      <c r="G26" s="2">
+        <v>44</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>126</v>
+      </c>
       <c r="I26" s="8"/>
       <c r="J26" s="8"/>
       <c r="K26" s="8"/>
@@ -1553,8 +1590,9 @@
     </row>
     <row r="27" spans="1:21" ht="22" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
-        <v>73</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="B27" s="7"/>
       <c r="C27" s="8"/>
       <c r="D27" s="8"/>
       <c r="E27" s="8"/>
@@ -1577,7 +1615,7 @@
     </row>
     <row r="28" spans="1:21" ht="22" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B28" s="7"/>
       <c r="C28" s="8"/>
@@ -1600,420 +1638,395 @@
       <c r="T28" s="5"/>
       <c r="U28" s="5"/>
     </row>
-    <row r="29" spans="1:21" ht="22" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B29" s="7"/>
-      <c r="C29" s="8"/>
-      <c r="D29" s="8"/>
-      <c r="E29" s="8"/>
-      <c r="F29" s="8"/>
-      <c r="G29" s="8"/>
-      <c r="H29" s="8"/>
-      <c r="I29" s="8"/>
-      <c r="J29" s="8"/>
-      <c r="K29" s="8"/>
-      <c r="L29" s="8"/>
-      <c r="M29" s="8"/>
-      <c r="N29" s="4"/>
-      <c r="O29" s="5"/>
-      <c r="P29" s="5"/>
-      <c r="Q29" s="5"/>
-      <c r="R29" s="5"/>
-      <c r="S29" s="5"/>
-      <c r="T29" s="5"/>
-      <c r="U29" s="5"/>
+        <v>22</v>
+      </c>
+      <c r="F29" s="6"/>
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F30" s="6"/>
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F31" s="6"/>
+        <v>24</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C31" s="2">
+        <v>700</v>
+      </c>
+      <c r="D31" s="2">
+        <v>700</v>
+      </c>
+      <c r="E31" s="2">
+        <v>700</v>
+      </c>
+      <c r="F31" s="2">
+        <v>700</v>
+      </c>
+      <c r="G31" s="2">
+        <v>700</v>
+      </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C32" s="2">
-        <v>700</v>
+        <v>2.25</v>
       </c>
       <c r="D32" s="2">
-        <v>700</v>
+        <v>2.25</v>
       </c>
       <c r="E32" s="2">
-        <v>700</v>
+        <v>2.25</v>
       </c>
       <c r="F32" s="2">
-        <v>700</v>
+        <v>2.25</v>
       </c>
       <c r="G32" s="2">
-        <v>700</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C33" s="2">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="D33" s="2">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="E33" s="2">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="F33" s="2">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="G33" s="2">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C34" s="2">
-        <v>2.4</v>
-      </c>
-      <c r="D34" s="2">
-        <v>2.4</v>
-      </c>
-      <c r="E34" s="2">
-        <v>2.4</v>
-      </c>
-      <c r="F34" s="2">
-        <v>2.4</v>
-      </c>
-      <c r="G34" s="2">
-        <v>2.4</v>
+        <v>28</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A36" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B36" s="2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="37" spans="1:12" ht="22" x14ac:dyDescent="0.3">
-      <c r="C37" s="9"/>
-      <c r="D37" s="7"/>
-      <c r="E37" s="7"/>
-      <c r="F37" s="7"/>
-      <c r="L37" s="1"/>
+    <row r="36" spans="1:12" ht="22" x14ac:dyDescent="0.3">
+      <c r="C36" s="9"/>
+      <c r="D36" s="7"/>
+      <c r="E36" s="7"/>
+      <c r="F36" s="7"/>
+      <c r="L36" s="1"/>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A37" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
-        <v>31</v>
+        <v>68</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>32</v>
+        <v>116</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>119</v>
+        <v>70</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>70</v>
+        <v>110</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
-        <v>71</v>
+        <v>33</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>112</v>
+        <v>83</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>72</v>
+        <v>35</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="B44" s="2">
+        <v>2.4</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B45" s="2">
-        <v>2.4</v>
+        <v>37</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B47" s="2">
-        <v>100</v>
+        <v>39</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="B50" s="2">
+        <v>148</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B51" s="2">
-        <v>148</v>
+        <v>110</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B52" s="2">
-        <v>110</v>
+        <v>117</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
-        <v>125</v>
+        <v>44</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B59" s="2" t="s">
-        <v>117</v>
+        <v>45</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="B60" s="2">
+        <v>31.6</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B61" s="2">
-        <v>31.6</v>
+        <v>47</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B62" s="2" t="s">
-        <v>72</v>
+        <v>48</v>
+      </c>
+      <c r="B62" s="2">
+        <v>42</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B63" s="2">
-        <v>42</v>
+        <v>49</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>118</v>
+        <v>84</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B69" s="2" t="s">
-        <v>86</v>
+        <v>55</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A77" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="B78" s="2">
+        <v>3450</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="B79" s="2">
-        <v>3450</v>
+        <v>65</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A80" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A81" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A82" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="B82" s="2" t="s">
+      <c r="A82" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="B82" s="14" t="s">
         <v>87</v>
-      </c>
-    </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A83" s="14" t="s">
-        <v>88</v>
-      </c>
-      <c r="B83" s="14" t="s">
-        <v>89</v>
       </c>
     </row>
   </sheetData>
